--- a/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen otros</t>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,64</t>
+          <t>4,22; 12,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 24,05</t>
+          <t>5,85; 24,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,89</t>
+          <t>6,31; 18,17</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 18,71</t>
+          <t>3,49; 17,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,05</t>
+          <t>4,59; 10,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,96</t>
+          <t>4,98; 11,44</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,72</t>
+          <t>4,78; 12,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,36</t>
+          <t>2,04; 7,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,89</t>
+          <t>4,34; 8,91</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,97</t>
+          <t>1,3; 5,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,97</t>
+          <t>5,28; 12,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,17</t>
+          <t>3,98; 8,25</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,58</t>
+          <t>4,74; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,5</t>
+          <t>6,0; 10,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,02</t>
+          <t>5,89; 9,2</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8741</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16699</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25440</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4944; 14125</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8209; 34537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16267; 46833</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13987</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18605</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32593</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6640; 33466</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11716; 27467</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22176; 50982</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15734</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23199</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9060; 24085</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3697; 14461</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16092; 33006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5342</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14858</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2182; 9848</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9563; 22737</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13887; 28761</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101432</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>31503; 62818</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45454; 79980</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>83732; 130841</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,04</t>
+          <t>4,26; 12,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 24,6</t>
+          <t>6,11; 25,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 18,17</t>
+          <t>6,38; 18,76</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 17,57</t>
+          <t>3,51; 17,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,77</t>
+          <t>4,73; 11,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 11,44</t>
+          <t>5,02; 12,05</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,7</t>
+          <t>4,37; 12,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,99</t>
+          <t>2,02; 7,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,88</t>
+          <t>1,5; 6,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,55</t>
+          <t>5,03; 12,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,25</t>
+          <t>4,03; 8,33</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,45</t>
+          <t>4,86; 9,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,56</t>
+          <t>5,81; 10,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,2</t>
+          <t>5,85; 9,15</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4944; 14125</t>
+          <t>4993; 14444</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8209; 34537</t>
+          <t>8579; 35815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16267; 46833</t>
+          <t>16429; 48332</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6640; 33466</t>
+          <t>6686; 33666</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11716; 27467</t>
+          <t>12068; 28115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22176; 50982</t>
+          <t>22347; 53676</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9060; 24085</t>
+          <t>8294; 24396</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3697; 14461</t>
+          <t>3655; 13515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16092; 33006</t>
+          <t>16074; 33013</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2182; 9848</t>
+          <t>2503; 10508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9563; 22737</t>
+          <t>9109; 22636</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13887; 28761</t>
+          <t>14037; 29025</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31503; 62818</t>
+          <t>32300; 64667</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45454; 79980</t>
+          <t>44031; 78467</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83732; 130841</t>
+          <t>83249; 130132</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,32</t>
+          <t>4,54; 14,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 25,51</t>
+          <t>4,35; 12,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 18,76</t>
+          <t>5,48; 11,46</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 17,67</t>
+          <t>4,76; 11,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,02</t>
+          <t>2,82; 8,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,05</t>
+          <t>4,62; 8,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,87</t>
+          <t>1,96; 7,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,46</t>
+          <t>6,59; 15,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,91</t>
+          <t>5,06; 10,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,28</t>
+          <t>5,12; 12,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,49</t>
+          <t>1,4; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,33</t>
+          <t>3,88; 8,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,73</t>
+          <t>5,5; 9,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,36</t>
+          <t>4,89; 8,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,15</t>
+          <t>5,63; 8,05</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>19788</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4993; 14444</t>
+          <t>5717; 17855</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8579; 35815</t>
+          <t>5266; 15318</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16429; 48332</t>
+          <t>13533; 28310</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>26857</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6686; 33666</t>
+          <t>11285; 26704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12068; 28115</t>
+          <t>5209; 15583</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22347; 53676</t>
+          <t>19492; 36281</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>23384</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8294; 24396</t>
+          <t>3208; 12991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3655; 13515</t>
+          <t>10286; 24600</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16074; 33013</t>
+          <t>16212; 32951</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>19304</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2503; 10508</t>
+          <t>8679; 20434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9109; 22636</t>
+          <t>2325; 10338</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14037; 29025</t>
+          <t>13035; 27334</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32300; 64667</t>
+          <t>38275; 63224</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44031; 78467</t>
+          <t>30744; 52096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83249; 130132</t>
+          <t>74610; 106578</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,54; 14,18</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,35; 12,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,48; 11,46</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,76; 11,26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,82; 8,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,62; 8,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,96; 7,92</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 15,75</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,06; 10,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,12; 12,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 6,21</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3,88; 8,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 9,08</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,89; 8,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,63; 8,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.08544670241652666</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.0745794946689729</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.08011946129078738</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10758</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9029</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19788</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04540667168941989</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.04349122083519272</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.05479493863786274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5717; 17855</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5266; 15318</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13533; 28310</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1418154634288392</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1265193973385293</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1146276764447986</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.0731773579019484</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05150615110501032</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.06369854965467799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>17358</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9498</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26857</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.04757400917453467</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02824368777632996</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.04623114051453282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>11285; 26704</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5209; 15583</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>19492; 36281</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1125790671050706</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.08450234170556002</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0860524073233551</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.04339483656930421</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.104150493080834</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.07303574022569168</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7115</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16269</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23384</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.01956492443341405</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.06585253931270793</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.05063332743151139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3208; 12991</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>10286; 24600</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16212; 32951</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.07922455696563709</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1574864722373489</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1029153302397142</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.08143822060000767</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.03309920040747889</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.05747750135819692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>13794</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5510</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19304</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.05124261901257244</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01396675246872841</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.03881067217365049</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>8679; 20434</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2325; 10338</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13035; 27334</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1206407260346561</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.0620994092711031</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.08138648707636213</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.07039256836535702</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.06416605638225517</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.06743982926273606</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>49026</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40307</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89332</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.05495578711370718</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.04894209517830649</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.0563257980998</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>38275; 63224</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>30744; 52096</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>74610; 106578</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.09077933455002261</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.08293435284411807</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.08045877047757023</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10758</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9029</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>19788</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>5717</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5266</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13533</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17855</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>15318</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>28310</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17358</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9498</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>26857</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>11285</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5209</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>19492</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>26704</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>15583</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>36281</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7115</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>16269</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>23384</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3208</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>10286</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>16212</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>12991</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>24600</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>32951</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>13794</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5510</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>19304</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>8679</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2325</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>13035</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>20434</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>10338</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>27334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>49026</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>40307</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>89332</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>38275</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>30744</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>74610</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>63224</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>52096</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>106578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>